--- a/audits/vaseline/vaseline_audit.xlsx
+++ b/audits/vaseline/vaseline_audit.xlsx
@@ -740,12 +740,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ungradable: 17 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 9. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 17 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 9. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, Caprylic/Capric Triglyceride, Glycol Stearate, Glyceryl Stearate, Copernicia Cerifera (Carnauba) Wax, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium Edta, Stearamide Amp, Hydroxystearic Acid, Sodium Ascorbyl Phosphate, Rutin, Palmitoyl Tripeptide-1, Palmitoyl Tetrapeptide-7, Phaseolus Lunatus (Green Bean) Seed Extract, Alpha-Isomethyl Ionone, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Caprylic/Capric Triglyceride, Glycol Stearate, Glyceryl Stearate, Copernicia Cerifera (Carnauba) Wax, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium Edta, Stearamide Amp, Hydroxystearic Acid, Sodium Ascorbyl Phosphate, Rutin, Palmitoyl Tripeptide-1, Palmitoyl Tetrapeptide-7, Phaseolus Lunatus (Green Bean) Seed Extract, Alpha-Isomethyl Ionone, Caramel.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ungradable: 6 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 6 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Dicaprylyl Ether, Vitis Vinifera (Grape) Seed Oil, Stearic Acid, Simmondsia Chinensis (Jojoba) Seed Oil, Tocopheryl Acetate, Alpha-Isomethyl Ionone.</t>
+          <t>D7: ungradable. Two or more unknown ingredients remain: Dicaprylyl Ether, Vitis Vinifera (Grape) Seed Oil, Stearic Acid, Simmondsia Chinensis (Jojoba) Seed Oil, Tocopheryl Acetate, Alpha-Isomethyl Ionone.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ungradable: 17 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 9. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 17 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 9. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, Caprylic/Capric Triglyceride, Glycol Stearate, Glyceryl Stearate, Copernicia Cerifera (Carnauba) Wax, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium Edta, Stearamide Amp, Hydroxystearic Acid, Sodium Ascorbyl Phosphate, Rutin, Palmitoyl Tripeptide-1, Palmitoyl Tetrapeptide-7, Phaseolus Lunatus (Green Bean) Seed Extract, Alpha-Isomethyl Ionone, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Caprylic/Capric Triglyceride, Glycol Stearate, Glyceryl Stearate, Copernicia Cerifera (Carnauba) Wax, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium Edta, Stearamide Amp, Hydroxystearic Acid, Sodium Ascorbyl Phosphate, Rutin, Palmitoyl Tripeptide-1, Palmitoyl Tetrapeptide-7, Phaseolus Lunatus (Green Bean) Seed Extract, Alpha-Isomethyl Ionone, Caramel.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Butyrospermum Parkii (Shea) Butter, Copernicia Cerifera (Carnauba) Wax, Isopropyl Myristate, Glyceryl Hydroxystearate, Hydroxystearic Acid, Ammonium Acryloyldimethyltaurate/Vp Copolymer, Stearic Acid, Sodium Ascorbyl Phosphate, Rutin, Palmitoyl Tripeptide-1, Palmitoyl Tetrapeptide-7, Phaseolus Lunatus (Green Bean) Seed Extract, Alpha-Isomethyl Ionone, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butyrospermum Parkii (Shea) Butter, Copernicia Cerifera (Carnauba) Wax, Isopropyl Myristate, Glyceryl Hydroxystearate, Hydroxystearic Acid, Ammonium Acryloyldimethyltaurate/Vp Copolymer, Stearic Acid, Sodium Ascorbyl Phosphate, Rutin, Palmitoyl Tripeptide-1, Palmitoyl Tetrapeptide-7, Phaseolus Lunatus (Green Bean) Seed Extract, Alpha-Isomethyl Ionone, Caramel.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 11. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 11. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Glyceryl Stearate, Polysorbate 80, Disodium Edta, Caramel, Theobroma Cacao (Cocoa) Seed Butter, Hydroxystearic Acid, Stearic Acid, Hexyl Cinnamal.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Glyceryl Stearate, Polysorbate 80, Disodium Edta, Caramel, Theobroma Cacao (Cocoa) Seed Butter, Hydroxystearic Acid, Stearic Acid, Hexyl Cinnamal.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1062,17 +1062,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>D7: ungradable. Unknown ingredient(s) remain after D1 to D6: White Petrolatum Usp.</t>
+          <t>D8: one unknown ingredient, Use Caution floor applied (White Petrolatum Usp).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1128,17 +1128,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s) in the printed list (Petrolatum, Fragrance); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Theobroma Cacao (Cocoa) Seed Butter.</t>
+          <t>D8: one unknown ingredient, Use Caution floor applied (Theobroma Cacao (Cocoa) Seed Butter). Higher tier from other flags kept.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1186,17 +1186,17 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>D7: ungradable. Unknown ingredient(s) remain after D1 to D6: White Petrolatum USP.</t>
+          <t>D8: one unknown ingredient, Use Caution floor applied (White Petrolatum USP).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ungradable: 6 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 8. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 6 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Silica Dimethyl Silylate, Calcium Sodium Borosilicate, Theobroma Cacao (Cocoa) Seed Butter, Tocopheryl Acetate, Tin Oxide (Ci 77861), Yellow 5 Lake (Ci 19140).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D7: ungradable. Two or more unknown ingredients remain: Silica Dimethyl Silylate, Calcium Sodium Borosilicate, Theobroma Cacao (Cocoa) Seed Butter, Tocopheryl Acetate, Tin Oxide (Ci 77861), Yellow 5 Lake (Ci 19140).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ungradable: 3 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 3 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ozokerite, Tocopheryl Acetate, Yellow 5 Lake (Ci 19140).</t>
+          <t>D7: ungradable. Two or more unknown ingredients remain: Ozokerite, Tocopheryl Acetate, Yellow 5 Lake (Ci 19140).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 9. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 9. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: STEARIC ACID, GLYCOL STEARATE, ISOPROPYL PALMITATE, ALOE BARBADENSIS LEAF JUICE POWDER, GLYCERYL STEARATE, TAPIOCA STARCH, DISODIUM EDTA, STEARAMIDE AMP, HELIANTHUS ANNUUS (SUNFLOWER) SEED OIL, HEXYL CINNAMAL.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: STEARIC ACID, GLYCOL STEARATE, ISOPROPYL PALMITATE, ALOE BARBADENSIS LEAF JUICE POWDER, GLYCERYL STEARATE, TAPIOCA STARCH, DISODIUM EDTA, STEARAMIDE AMP, HELIANTHUS ANNUUS (SUNFLOWER) SEED OIL, HEXYL CINNAMAL.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 13. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 13. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: STEARIC ACID, GLYCOL STEARATE, ISOPROPYL MYRISTATE, SODIUM HYDROXYPROPYL STARCH PHOSPHATE, HELIANTHUS ANNUUS (SUNFLOWER) SEED OIL, THEOBROMA CACAO (COCOA) SEED BUTTER, GLYCERYL STEARATE, MAGNESIUM ALUMINUM SILICATE, STEARAMIDE AMP, DISODIUM EDTA, HEXYL CINNAMAL, CARAMEL.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: STEARIC ACID, GLYCOL STEARATE, ISOPROPYL MYRISTATE, SODIUM HYDROXYPROPYL STARCH PHOSPHATE, HELIANTHUS ANNUUS (SUNFLOWER) SEED OIL, THEOBROMA CACAO (COCOA) SEED BUTTER, GLYCERYL STEARATE, MAGNESIUM ALUMINUM SILICATE, STEARAMIDE AMP, DISODIUM EDTA, HEXYL CINNAMAL, CARAMEL.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1516,12 +1516,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ungradable: 15 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 12. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 15 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 12. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: STEARIC ACID, ISOPROPYL MYRISTATE, AVENA SATIVA (OAT) STRAW EXTRACT, GLYCOL STEARATE, GLYCERYL STEARATE, TAPIOCA STARCH, MAGNESIUM ALUMINUM SILICATE, HELIANTHUS ANNUUS (SUNFLOWER) SEED OIL, ACRYLATES/C10-30 ALKYL ACRYLATE CROSSPOLYMER, DISODIUM EDTA, STEARAMIDE AMP, ALPHA-ISOMETHYL IONONE, CINNAMYL ALCOHOL, CITRONELLOL, HEXYL CINNAMAL.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: STEARIC ACID, ISOPROPYL MYRISTATE, AVENA SATIVA (OAT) STRAW EXTRACT, GLYCOL STEARATE, GLYCERYL STEARATE, TAPIOCA STARCH, MAGNESIUM ALUMINUM SILICATE, HELIANTHUS ANNUUS (SUNFLOWER) SEED OIL, ACRYLATES/C10-30 ALKYL ACRYLATE CROSSPOLYMER, DISODIUM EDTA, STEARAMIDE AMP, ALPHA-ISOMETHYL IONONE, CINNAMYL ALCOHOL, CITRONELLOL, HEXYL CINNAMAL.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 12. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 12. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: STEARIC ACID, ISOPROPYL MYRISTATE, GLYCERYL STEARATE, GLYCOL STEARATE, TAPIOCA STARCH, MAGNESIUM ALUMINUM SILICATE, ACRYLATES/C10-30 ALKYL ACRYLATE CROSSPOLYMER, DISODIUM EDTA, STEARAMIDE AMP, HELIANTHUS ANNUUS (SUNFLOWER) SEED OIL, LAVANDULA ANGUSTIFOLIA (LAVENDER) FLOWER EXTRACT, CITRONELLOL.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: STEARIC ACID, ISOPROPYL MYRISTATE, GLYCERYL STEARATE, GLYCOL STEARATE, TAPIOCA STARCH, MAGNESIUM ALUMINUM SILICATE, ACRYLATES/C10-30 ALKYL ACRYLATE CROSSPOLYMER, DISODIUM EDTA, STEARAMIDE AMP, HELIANTHUS ANNUUS (SUNFLOWER) SEED OIL, LAVANDULA ANGUSTIFOLIA (LAVENDER) FLOWER EXTRACT, CITRONELLOL.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Audit notes: Ingredient list as printed on the product page ends mid-word at 'PROPYLP'. The page's own data layer carries the same truncated string, so the remainder of the list is not captured. Manual re-check needed against the physical package or the brand's SmartLabel before grading is final. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: STEARIC ACID, ISOPROPYL PALMITATE, GLYCOL STEARATE, HELIANTHUS ANNUUS (SUNFLOWER) SEED OIL, GLYCERYL STEARATE, ACRYLATES/C10-30 ALKYL ACRYLATE CROSSPOLYMER, PROPYLP.</t>
+          <t>Audit notes: Ingredient list as printed on the product page ends mid-word at 'PROPYLP'. The page's own data layer carries the same truncated string, so the remainder of the list is not captured. Manual re-check needed against the physical package or the brand's SmartLabel before grading is final. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: STEARIC ACID, ISOPROPYL PALMITATE, GLYCOL STEARATE, HELIANTHUS ANNUUS (SUNFLOWER) SEED OIL, GLYCERYL STEARATE, ACRYLATES/C10-30 ALKYL ACRYLATE CROSSPOLYMER, PROPYLP.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ungradable: 15 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 15 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, Isopropyl Palmitate, Glycol Stearate, Glyceryl Stearate, Butyrospermum Parkii (Shea) Butter, Theobroma Cacao (Cocoa) Seed Butter, Magnesium Aluminum Silicate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Prunus Amygdalus Dulcis (Sweet Almond) Oil, Disodium EDTA, Stearamide AMP, Helianthus Annuus (Sunflower) Seed Oil, Alpha-Isomethyl Ionone, Hexyl Cinnamal, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Isopropyl Palmitate, Glycol Stearate, Glyceryl Stearate, Butyrospermum Parkii (Shea) Butter, Theobroma Cacao (Cocoa) Seed Butter, Magnesium Aluminum Silicate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Prunus Amygdalus Dulcis (Sweet Almond) Oil, Disodium EDTA, Stearamide AMP, Helianthus Annuus (Sunflower) Seed Oil, Alpha-Isomethyl Ionone, Hexyl Cinnamal, Caramel.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ungradable: 13 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 11. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 13 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 11. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, Glycol Stearate, Isopropyl Palmitate, Glyceryl Stearate, Tapioca Starch, Disodium EDTA, Menthol, Stearamide AMP, Helianthus Annuus (Sunflower) Seed Oil, Benzyl Salicylate, Hexyl Cinnamal, Blue 1 (CI 42090), Yellow 5 (CI 19140).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Glycol Stearate, Isopropyl Palmitate, Glyceryl Stearate, Tapioca Starch, Disodium EDTA, Menthol, Stearamide AMP, Helianthus Annuus (Sunflower) Seed Oil, Benzyl Salicylate, Hexyl Cinnamal, Blue 1 (CI 42090), Yellow 5 (CI 19140).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ungradable: 24 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 15. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 24 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 15. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, Hydrogenated Polyisobutene, Ethylhexyl Cocoate, Glycol Stearate, Hydrogenated Didecene, Butyrospermum Parkii Butter, Caramel, Dimethiconol, Disodium EDTA, Disteareth-75 IPDI, Glyceryl Stearate, Hydrogenated Polydecene, Isohexadecane, Isostearic Acid, Maltodextrin, Microcrystalline Wax, Diisostearate, Polysorbate 80, Potato Starch Modified, Sodium Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Sorbitan Monooleate, Stearamide AMP, Theobroma Cacao Seed Butter, CI 19140.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Hydrogenated Polyisobutene, Ethylhexyl Cocoate, Glycol Stearate, Hydrogenated Didecene, Butyrospermum Parkii Butter, Caramel, Dimethiconol, Disodium EDTA, Disteareth-75 IPDI, Glyceryl Stearate, Hydrogenated Polydecene, Isohexadecane, Isostearic Acid, Maltodextrin, Microcrystalline Wax, Diisostearate, Polysorbate 80, Potato Starch Modified, Sodium Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Sorbitan Monooleate, Stearamide AMP, Theobroma Cacao Seed Butter, CI 19140.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, Isopropyl Myristate, Glyceryl Stearate, Glycol Stearate, Tapioca Starch, Magnesium Aluminum Silicate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Stearamide AMP, Helianthus Annuus (Sunflower) Seed Oil.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Isopropyl Myristate, Glyceryl Stearate, Glycol Stearate, Tapioca Starch, Magnesium Aluminum Silicate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Stearamide AMP, Helianthus Annuus (Sunflower) Seed Oil.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 11. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 11. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, Isopropyl Palmitate, Glycol Stearate, Glyceryl Stearate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Stearamide AMP, Disodium EDTA, Helianthus Annuus (Sunflower) Seed Oil.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Isopropyl Palmitate, Glycol Stearate, Glyceryl Stearate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Stearamide AMP, Disodium EDTA, Helianthus Annuus (Sunflower) Seed Oil.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -2044,17 +2044,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1. Escalation: carcinogen in leave-on.</t>
+          <t>1 flagged ingredient(s) in the printed list (Petrolatum); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Yellow 5 Lake.</t>
+          <t>D8: one unknown ingredient, Use Caution floor applied (Yellow 5 Lake). Higher tier from other flags kept.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Ungradable: 3 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 3 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Flavor, Red 30 Lake, Yellow 5 Lake.</t>
+          <t>D7: ungradable. Two or more unknown ingredients remain: Flavor, Red 30 Lake, Yellow 5 Lake.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Ungradable: 3 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 3 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Identical printed text on 1 other product(s): Vaseline® Lip Therapy® Crème Brûlée Mini. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Flavor, Theobroma Cacao (Cocoa) Seed Butter, Yellow 5 Lake.</t>
+          <t>Identical printed text on 1 other product(s): Vaseline® Lip Therapy® Crème Brûlée Mini. D7: ungradable. Two or more unknown ingredients remain: Flavor, Theobroma Cacao (Cocoa) Seed Butter, Yellow 5 Lake.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Ungradable: 3 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 3 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Identical printed text on 1 other product(s): Vaseline® Lip Therapy® Cocoa Butter Mini. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Flavor, Theobroma Cacao (Cocoa) Seed Butter, Yellow 5 Lake.</t>
+          <t>Identical printed text on 1 other product(s): Vaseline® Lip Therapy® Cocoa Butter Mini. D7: ungradable. Two or more unknown ingredients remain: Flavor, Theobroma Cacao (Cocoa) Seed Butter, Yellow 5 Lake.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Isopropyl Myristate, Sorbitan Isostearate, Tapioca Starch, Stearic Acid, Ammonium Acryloyldimethyltaurate/VP Copolymer, Disodium EDTA, Aloe Barbadensis Leaf Juice Powder.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Isopropyl Myristate, Sorbitan Isostearate, Tapioca Starch, Stearic Acid, Ammonium Acryloyldimethyltaurate/VP Copolymer, Disodium EDTA, Aloe Barbadensis Leaf Juice Powder.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Isopropyl Myristate, Sorbitan Isostearate, Tapioca Starch, Stearic Acid, Ammonium Acryloyldimethyltaurate/Vp Copolymer, Disodium Edta, Theobroma Cacao (Cocoa) Seed Butter.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Isopropyl Myristate, Sorbitan Isostearate, Tapioca Starch, Stearic Acid, Ammonium Acryloyldimethyltaurate/Vp Copolymer, Disodium Edta, Theobroma Cacao (Cocoa) Seed Butter.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Microcrystalline Wax, Caprylic/Capric Triglyceride, Ricinus Communis (Castor) Seed Oil, Polyglyceryl-3 Distearate, Butyrospermum Parkii (Shea) Butter, Copernicia Cerifera (Carnauba) Wax, C20-40 Alkyl Stearate, Tocopheryl Acetate.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Microcrystalline Wax, Caprylic/Capric Triglyceride, Ricinus Communis (Castor) Seed Oil, Polyglyceryl-3 Distearate, Butyrospermum Parkii (Shea) Butter, Copernicia Cerifera (Carnauba) Wax, C20-40 Alkyl Stearate, Tocopheryl Acetate.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Audit notes: Printed carnauba INCI reads 'Camauba' on the page; kept as printed. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Microcrystalline Wax, Caprylic/Capric Triglyceride, Ricinus Communis (Castor) Seed Oil, Polyglyceryl-3 Distearate, Butyrospermum Parkii (Shea) Butter, Copernicia Cerifera (Camauba) Wax, C20-40 Alkyl Stearate, Tocopheryl Acetate, Rose Flower Oil, Olea Europaea (Olive) Fruit Oil, Prunus Amygdalus Dulcis (Sweet Almond) Oil, Rubus Idaeus (Raspberry) Fruit Extract, Red 7 Lake (Ci 15850).</t>
+          <t>Audit notes: Printed carnauba INCI reads 'Camauba' on the page; kept as printed. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Microcrystalline Wax, Caprylic/Capric Triglyceride, Ricinus Communis (Castor) Seed Oil, Polyglyceryl-3 Distearate, Butyrospermum Parkii (Shea) Butter, Copernicia Cerifera (Camauba) Wax, C20-40 Alkyl Stearate, Tocopheryl Acetate, Rose Flower Oil, Olea Europaea (Olive) Fruit Oil, Prunus Amygdalus Dulcis (Sweet Almond) Oil, Rubus Idaeus (Raspberry) Fruit Extract, Red 7 Lake (Ci 15850).</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Microcrystalline Wax, Caprylic/Capric Triglyceride, Ricinus Communis (Castor) Seed Oil, Polyglyceryl-3 Distearate, Butyrospermum Parkii (Shea) Butter, Copernicia Cerifera (Carnauba) Wax, C20-40 Alkyl Stearate, Tocopheryl Acetate, Persea Gratissima (Avocado) Oil, Camellia Sinensis Leaf Extract, Aloe Barbadensis Leaf Extract.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Microcrystalline Wax, Caprylic/Capric Triglyceride, Ricinus Communis (Castor) Seed Oil, Polyglyceryl-3 Distearate, Butyrospermum Parkii (Shea) Butter, Copernicia Cerifera (Carnauba) Wax, C20-40 Alkyl Stearate, Tocopheryl Acetate, Persea Gratissima (Avocado) Oil, Camellia Sinensis Leaf Extract, Aloe Barbadensis Leaf Extract.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Microcrystalline Wax, Caprylic Triglyceride, Ricinus Communis (Castor) Seed Oil, Polyglyceryl-3 Distearate, Shea Butter, Cocoa Seed Butter, Carnauba Wax, C20-40 Alkyl Stearate, Tocopheryl Acetate, Jojoba Seed Oil, Camellia Sinensis Leaf Extract, Avocado Fruit Extract, Macadamia Integrifolia Seed Oil. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Microcrystalline Wax, Caprylic Triglyceride, Ricinus Communis (Castor) Seed Oil, Polyglyceryl-3 Distearate, Shea Butter, Cocoa Seed Butter, Carnauba Wax, C20-40 Alkyl Stearate, Tocopheryl Acetate, Jojoba Seed Oil, Camellia Sinensis Leaf Extract, Avocado Fruit Extract, Macadamia Integrifolia Seed Oil. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Flavor (Aroma), Red 30 (Ci 73360).</t>
+          <t>D7: ungradable. Two or more unknown ingredients remain: Flavor (Aroma), Red 30 (Ci 73360).</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Audit notes: Product name printed on the page h1 omits the Vaseline brand prefix; listing name used. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Hydrogenated Styrene/Butadiene Copolymer, Helianthus Annuus (Sunflower) Seed Oil, Stearic Acid, Theobroma Cacao (Cocoa) Seed Butter, Calcium Sodium Borosilicate, Benzyl Benzoate, Hexyl Cinnamal, Tin Oxide (CI 77861).</t>
+          <t>Audit notes: Product name printed on the page h1 omits the Vaseline brand prefix; listing name used. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D7: ungradable. Two or more unknown ingredients remain: Hydrogenated Styrene/Butadiene Copolymer, Helianthus Annuus (Sunflower) Seed Oil, Stearic Acid, Theobroma Cacao (Cocoa) Seed Butter, Calcium Sodium Borosilicate, Benzyl Benzoate, Hexyl Cinnamal, Tin Oxide (CI 77861).</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2886,12 +2886,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 8. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Audit notes: Product name printed on the page h1 omits the Vaseline brand prefix; listing name used. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Hydrogenated Styrene/Butadiene Copolymer, Helianthus Annuus (Sunflower) Seed Oil, Stearic Acid, Theobroma Cacao (Cocoa) Seed Butter, Calcium Sodium Borosilicate, Calcium Aluminum Borosilicate, Benzyl Benzoate, Hexyl Cinnamal, Tin Oxide (CI 77861).</t>
+          <t>Audit notes: Product name printed on the page h1 omits the Vaseline brand prefix; listing name used. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D7: ungradable. Two or more unknown ingredients remain: Hydrogenated Styrene/Butadiene Copolymer, Helianthus Annuus (Sunflower) Seed Oil, Stearic Acid, Theobroma Cacao (Cocoa) Seed Butter, Calcium Sodium Borosilicate, Calcium Aluminum Borosilicate, Benzyl Benzoate, Hexyl Cinnamal, Tin Oxide (CI 77861).</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Hydrogenated Styrene/Butadiene Copolymer, Theobroma Cacao (Cocoa) Seed Butter.</t>
+          <t>D7: ungradable. Two or more unknown ingredients remain: Hydrogenated Styrene/Butadiene Copolymer, Theobroma Cacao (Cocoa) Seed Butter.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Ungradable: 15 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 15 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Isohexadecane, Stearic Acid, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium Edta, Helianthus Annuus (Sunflower) Seed Oil, Glycine, Sodium Pca, Cystine, Rutin, Palmitoyl Tripeptide-1, Palmitoyl Tetrapeptide-7, Phaseolus Lunatus (Green Bean) Seed Extract, Benzyl Salicylate, Citronellol, Hexyl Cinnamal.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Isohexadecane, Stearic Acid, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium Edta, Helianthus Annuus (Sunflower) Seed Oil, Glycine, Sodium Pca, Cystine, Rutin, Palmitoyl Tripeptide-1, Palmitoyl Tetrapeptide-7, Phaseolus Lunatus (Green Bean) Seed Extract, Benzyl Salicylate, Citronellol, Hexyl Cinnamal.</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3634,12 +3634,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Ungradable: 13 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 13 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Isohexadecane, Stearic Acid, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium Edta, Helianthus Annuus (Sunflower) Seed Oil, Glycine, Sodium Pca, Cystine, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, Benzyl Salicylate, Citronellol, Hexyl Cinnamal.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Isohexadecane, Stearic Acid, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium Edta, Helianthus Annuus (Sunflower) Seed Oil, Glycine, Sodium Pca, Cystine, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, Benzyl Salicylate, Citronellol, Hexyl Cinnamal.</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">

--- a/audits/vaseline/vaseline_audit.xlsx
+++ b/audits/vaseline/vaseline_audit.xlsx
@@ -984,17 +984,17 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Dimethicone [2,6] / Dipropylene Glycol [2] / Ceteth-20 [1,4,5] (inferred: -eth ethoxylate) / Phenoxyethanol [1,2,4,5,8] / Petrolatum [1] / Fragrance (Parfum) [1,2,4,8] (fragrance without disclosure) / Methylparaben [2,4] / Carbomer [1,4,6] / Propylparaben [2,4] / Coumarin [4,8] (natural component, no source essential oil listed: full flag) / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
+          <t>Dimethicone [2,6] / Dipropylene Glycol [2] / Ceteth-20 [1,4,5] (inferred: -eth ethoxylate) / Phenoxyethanol [1,2,4,5,8] / Petrolatum [1] / Fragrance (Parfum) [1,2,4,8] (fragrance without disclosure) / Methylparaben [2,4] / Polysorbate 80 [1,2,4,5] / Carbomer [1,4,6] / Propylparaben [2,4] / Coumarin [4,8] (natural component, no source essential oil listed: full flag) / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Glyceryl Stearate, Polysorbate 80, Disodium Edta, Caramel, Theobroma Cacao (Cocoa) Seed Butter, Hydroxystearic Acid, Stearic Acid, Hexyl Cinnamal</t>
+          <t>unknown — manual review needed: Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Glyceryl Stearate, Disodium Edta, Caramel, Theobroma Cacao (Cocoa) Seed Butter, Hydroxystearic Acid, Stearic Acid, Hexyl Cinnamal</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 11. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 12. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Glyceryl Stearate, Polysorbate 80, Disodium Edta, Caramel, Theobroma Cacao (Cocoa) Seed Butter, Hydroxystearic Acid, Stearic Acid, Hexyl Cinnamal.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Glyceryl Stearate, Disodium Edta, Caramel, Theobroma Cacao (Cocoa) Seed Butter, Hydroxystearic Acid, Stearic Acid, Hexyl Cinnamal.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>White Petrolatum Usp [1]</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>unknown — manual review needed: White Petrolatum Usp</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>D8: one unknown ingredient, Use Caution floor applied (White Petrolatum Usp).</t>
-        </is>
-      </c>
+          <t>1 flagged ingredient(s) in the printed list (White Petrolatum Usp); tier applies to the printed subset only. Escalation: carcinogen in leave-on.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>complete</t>
@@ -1170,30 +1170,30 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>White Petrolatum USP [1]</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>unknown — manual review needed: White Petrolatum USP</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 1 unknown ingredient(s) not in reference.</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>D8: one unknown ingredient, Use Caution floor applied (White Petrolatum USP).</t>
-        </is>
-      </c>
+          <t>1 flagged ingredient(s) in the printed list (White Petrolatum USP); tier applies to the printed subset only. Escalation: carcinogen in leave-on.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>complete</t>
@@ -1826,17 +1826,17 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Dimethicone [2,6] / Cyclopentasiloxane [1,2,6] / BHT [1,2] / Cyclomethicone [1,2,6] / Methylparaben [2,4] / Paraffin [1] / Parfum [1,2,4,8] (fragrance without disclosure) / PEG/PPG-20/15 Dimethicone [2,6] (inferred: silicone) / PEG-80 [1,2,4,5] (inferred: PEG-) / PEG-90 [1,2,4,5] (inferred: PEG-) / Phenoxyethanol [1,2,4,5,8] / Propylparaben [2,4] / Steareth-75 [1,4,5] (inferred: -eth ethoxylate) / Triethanolamine [1,4]</t>
+          <t>Petrolatum [1] / Dimethicone [2,6] / Cyclopentasiloxane [1,2,6] / BHT [1,2] / Cyclomethicone [1,2,6] / Methylparaben [2,4] / Paraffin [1] / Parfum [1,2,4,8] (fragrance without disclosure) / PEG/PPG-20/15 Dimethicone [2,6] (inferred: silicone) / PEG-80 [1,2,4,5] (inferred: PEG-) / PEG-90 [1,2,4,5] (inferred: PEG-) / Phenoxyethanol [1,2,4,5,8] / Polysorbate 80 [1,2,4,5] / Propylparaben [2,4] / Steareth-75 [1,4,5] (inferred: -eth ethoxylate) / Triethanolamine [1,4]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Stearic Acid, Hydrogenated Polyisobutene, Ethylhexyl Cocoate, Glycol Stearate, Hydrogenated Didecene, Butyrospermum Parkii Butter, Caramel, Dimethiconol, Disodium EDTA, Disteareth-75 IPDI, Glyceryl Stearate, Hydrogenated Polydecene, Isohexadecane, Isostearic Acid, Maltodextrin, Microcrystalline Wax, Diisostearate, Polysorbate 80, Potato Starch Modified, Sodium Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Sorbitan Monooleate, Stearamide AMP, Theobroma Cacao Seed Butter, CI 19140</t>
+          <t>unknown — manual review needed: Stearic Acid, Hydrogenated Polyisobutene, Ethylhexyl Cocoate, Glycol Stearate, Hydrogenated Didecene, Butyrospermum Parkii Butter, Caramel, Dimethiconol, Disodium EDTA, Disteareth-75 IPDI, Glyceryl Stearate, Hydrogenated Polydecene, Isohexadecane, Isostearic Acid, Maltodextrin, Microcrystalline Wax, Diisostearate, Potato Starch Modified, Sodium Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Sorbitan Monooleate, Stearamide AMP, Theobroma Cacao Seed Butter, CI 19140</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ungradable: 24 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 15. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 23 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 16. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Hydrogenated Polyisobutene, Ethylhexyl Cocoate, Glycol Stearate, Hydrogenated Didecene, Butyrospermum Parkii Butter, Caramel, Dimethiconol, Disodium EDTA, Disteareth-75 IPDI, Glyceryl Stearate, Hydrogenated Polydecene, Isohexadecane, Isostearic Acid, Maltodextrin, Microcrystalline Wax, Diisostearate, Polysorbate 80, Potato Starch Modified, Sodium Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Sorbitan Monooleate, Stearamide AMP, Theobroma Cacao Seed Butter, CI 19140.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Hydrogenated Polyisobutene, Ethylhexyl Cocoate, Glycol Stearate, Hydrogenated Didecene, Butyrospermum Parkii Butter, Caramel, Dimethiconol, Disodium EDTA, Disteareth-75 IPDI, Glyceryl Stearate, Hydrogenated Polydecene, Isohexadecane, Isostearic Acid, Maltodextrin, Microcrystalline Wax, Diisostearate, Potato Starch Modified, Sodium Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Sorbitan Monooleate, Stearamide AMP, Theobroma Cacao Seed Butter, CI 19140.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">

--- a/audits/vaseline/vaseline_audit.xlsx
+++ b/audits/vaseline/vaseline_audit.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -740,17 +740,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ungradable: 17 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 9. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>9 flagged ingredient(s) in the printed list (Dimethicone, Peg-100 Stearate, Petrolatum); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Caprylic/Capric Triglyceride, Glycol Stearate, Glyceryl Stearate, Copernicia Cerifera (Carnauba) Wax, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium Edta, Stearamide Amp, Hydroxystearic Acid, Sodium Ascorbyl Phosphate, Rutin, Palmitoyl Tripeptide-1, Palmitoyl Tetrapeptide-7, Phaseolus Lunatus (Green Bean) Seed Extract, Alpha-Isomethyl Ionone, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -806,17 +806,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ungradable: 6 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Mineral Oil, Fragrance (Parfum), Farnesol); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>D7: ungradable. Two or more unknown ingredients remain: Dicaprylyl Ether, Vitis Vinifera (Grape) Seed Oil, Stearic Acid, Simmondsia Chinensis (Jojoba) Seed Oil, Tocopheryl Acetate, Alpha-Isomethyl Ionone.</t>
+          <t>6 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -872,17 +872,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ungradable: 17 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 9. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>9 flagged ingredient(s) in the printed list (Dimethicone, Peg-100 Stearate, Petrolatum); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Caprylic/Capric Triglyceride, Glycol Stearate, Glyceryl Stearate, Copernicia Cerifera (Carnauba) Wax, Tapioca Starch, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium Edta, Stearamide Amp, Hydroxystearic Acid, Sodium Ascorbyl Phosphate, Rutin, Palmitoyl Tripeptide-1, Palmitoyl Tetrapeptide-7, Phaseolus Lunatus (Green Bean) Seed Extract, Alpha-Isomethyl Ionone, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -938,17 +938,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>10 flagged ingredient(s) in the printed list (Dimethicone, Petrolatum, Dimethicone Crosspolymer); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butyrospermum Parkii (Shea) Butter, Copernicia Cerifera (Carnauba) Wax, Isopropyl Myristate, Glyceryl Hydroxystearate, Hydroxystearic Acid, Ammonium Acryloyldimethyltaurate/Vp Copolymer, Stearic Acid, Sodium Ascorbyl Phosphate, Rutin, Palmitoyl Tripeptide-1, Palmitoyl Tetrapeptide-7, Phaseolus Lunatus (Green Bean) Seed Extract, Alpha-Isomethyl Ionone, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1004,17 +1004,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 12. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>12 flagged ingredient(s) in the printed list (Dimethicone, Dipropylene Glycol, Ceteth-20); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Sodium Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Glyceryl Stearate, Disodium Edta, Caramel, Theobroma Cacao (Cocoa) Seed Butter, Hydroxystearic Acid, Stearic Acid, Hexyl Cinnamal.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s) in the printed list (Petrolatum, Fragrance); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s) in the printed list (Petrolatum, Fragrance); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>D8: one unknown ingredient, Use Caution floor applied (Theobroma Cacao (Cocoa) Seed Butter). Higher tier from other flags kept.</t>
+          <t>1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1252,17 +1252,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ungradable: 6 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>8 flagged ingredient(s) in the printed list (Petrolatum, Paraffin, Polyethylene); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D7: ungradable. Two or more unknown ingredients remain: Silica Dimethyl Silylate, Calcium Sodium Borosilicate, Theobroma Cacao (Cocoa) Seed Butter, Tocopheryl Acetate, Tin Oxide (Ci 77861), Yellow 5 Lake (Ci 19140).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). 6 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1318,17 +1318,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ungradable: 3 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s) in the printed list (Petrolatum, Paraffin); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>D7: ungradable. Two or more unknown ingredients remain: Ozokerite, Tocopheryl Acetate, Yellow 5 Lake (Ci 19140).</t>
+          <t>3 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1384,17 +1384,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 9. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>9 flagged ingredient(s) in the printed list (PETROLATUM, TRIETHANOLAMINE, PHENOXYETHANOL); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: STEARIC ACID, GLYCOL STEARATE, ISOPROPYL PALMITATE, ALOE BARBADENSIS LEAF JUICE POWDER, GLYCERYL STEARATE, TAPIOCA STARCH, DISODIUM EDTA, STEARAMIDE AMP, HELIANTHUS ANNUUS (SUNFLOWER) SEED OIL, HEXYL CINNAMAL.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 13. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>13 flagged ingredient(s) in the printed list (PETROLATUM, DIMETHICONE, BUTYLENE GLYCOL); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: STEARIC ACID, GLYCOL STEARATE, ISOPROPYL MYRISTATE, SODIUM HYDROXYPROPYL STARCH PHOSPHATE, HELIANTHUS ANNUUS (SUNFLOWER) SEED OIL, THEOBROMA CACAO (COCOA) SEED BUTTER, GLYCERYL STEARATE, MAGNESIUM ALUMINUM SILICATE, STEARAMIDE AMP, DISODIUM EDTA, HEXYL CINNAMAL, CARAMEL.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1516,17 +1516,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ungradable: 15 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 12. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>12 flagged ingredient(s) in the printed list (DIMETHICONE, PEG-100 STEARATE, PETROLATUM); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: STEARIC ACID, ISOPROPYL MYRISTATE, AVENA SATIVA (OAT) STRAW EXTRACT, GLYCOL STEARATE, GLYCERYL STEARATE, TAPIOCA STARCH, MAGNESIUM ALUMINUM SILICATE, HELIANTHUS ANNUUS (SUNFLOWER) SEED OIL, ACRYLATES/C10-30 ALKYL ACRYLATE CROSSPOLYMER, DISODIUM EDTA, STEARAMIDE AMP, ALPHA-ISOMETHYL IONONE, CINNAMYL ALCOHOL, CITRONELLOL, HEXYL CINNAMAL.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1582,17 +1582,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 12. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>12 flagged ingredient(s) in the printed list (MINERAL OIL, DIMETHICONE, PEG-100 STEARATE); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: STEARIC ACID, ISOPROPYL MYRISTATE, GLYCERYL STEARATE, GLYCOL STEARATE, TAPIOCA STARCH, MAGNESIUM ALUMINUM SILICATE, ACRYLATES/C10-30 ALKYL ACRYLATE CROSSPOLYMER, DISODIUM EDTA, STEARAMIDE AMP, HELIANTHUS ANNUUS (SUNFLOWER) SEED OIL, LAVANDULA ANGUSTIFOLIA (LAVENDER) FLOWER EXTRACT, CITRONELLOL.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (PEG-100 STEARATE, DIMETHICONE, MINERAL OIL); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Audit notes: Ingredient list as printed on the product page ends mid-word at 'PROPYLP'. The page's own data layer carries the same truncated string, so the remainder of the list is not captured. Manual re-check needed against the physical package or the brand's SmartLabel before grading is final. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: STEARIC ACID, ISOPROPYL PALMITATE, GLYCOL STEARATE, HELIANTHUS ANNUUS (SUNFLOWER) SEED OIL, GLYCERYL STEARATE, ACRYLATES/C10-30 ALKYL ACRYLATE CROSSPOLYMER, PROPYLP.</t>
+          <t>Audit notes: Ingredient list as printed on the product page ends mid-word at 'PROPYLP'. The page's own data layer carries the same truncated string, so the remainder of the list is not captured. Manual re-check needed against the physical package or the brand's SmartLabel before grading is final. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1714,17 +1714,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ungradable: 15 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>10 flagged ingredient(s) in the printed list (Petrolatum, Dimethicone, Triethanolamine); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Isopropyl Palmitate, Glycol Stearate, Glyceryl Stearate, Butyrospermum Parkii (Shea) Butter, Theobroma Cacao (Cocoa) Seed Butter, Magnesium Aluminum Silicate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Prunus Amygdalus Dulcis (Sweet Almond) Oil, Disodium EDTA, Stearamide AMP, Helianthus Annuus (Sunflower) Seed Oil, Alpha-Isomethyl Ionone, Hexyl Cinnamal, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ungradable: 13 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 11. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>11 flagged ingredient(s) in the printed list (Petrolatum, Triethanolamine, Dimethicone); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Glycol Stearate, Isopropyl Palmitate, Glyceryl Stearate, Tapioca Starch, Disodium EDTA, Menthol, Stearamide AMP, Helianthus Annuus (Sunflower) Seed Oil, Benzyl Salicylate, Hexyl Cinnamal, Blue 1 (CI 42090), Yellow 5 (CI 19140).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 13 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1846,17 +1846,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ungradable: 23 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 16. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>16 flagged ingredient(s) in the printed list (Petrolatum, Dimethicone, Cyclopentasiloxane); tier applies to the printed subset only. 23 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Hydrogenated Polyisobutene, Ethylhexyl Cocoate, Glycol Stearate, Hydrogenated Didecene, Butyrospermum Parkii Butter, Caramel, Dimethiconol, Disodium EDTA, Disteareth-75 IPDI, Glyceryl Stearate, Hydrogenated Polydecene, Isohexadecane, Isostearic Acid, Maltodextrin, Microcrystalline Wax, Diisostearate, Potato Starch Modified, Sodium Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Sorbitan Monooleate, Stearamide AMP, Theobroma Cacao Seed Butter, CI 19140.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 23 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1912,17 +1912,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>10 flagged ingredient(s) in the printed list (Mineral Oil (Huile Minérale), Dimethicone, PEG-100 Stearate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Isopropyl Myristate, Glyceryl Stearate, Glycol Stearate, Tapioca Starch, Magnesium Aluminum Silicate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Stearamide AMP, Helianthus Annuus (Sunflower) Seed Oil.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1978,17 +1978,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 11. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>11 flagged ingredient(s) in the printed list (PEG-100 Stearate, Dimethicone, Mineral Oil (Huile Minérale)); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Isopropyl Palmitate, Glycol Stearate, Glyceryl Stearate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Stearamide AMP, Disodium EDTA, Helianthus Annuus (Sunflower) Seed Oil.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2044,12 +2044,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Petrolatum); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>1 flagged ingredient(s) in the printed list (Petrolatum); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>D8: one unknown ingredient, Use Caution floor applied (Yellow 5 Lake). Higher tier from other flags kept.</t>
+          <t>1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -2110,17 +2110,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Ungradable: 3 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1. Escalation: carcinogen in leave-on.</t>
+          <t>1 flagged ingredient(s) in the printed list (Petrolatum); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>D7: ungradable. Two or more unknown ingredients remain: Flavor, Red 30 Lake, Yellow 5 Lake.</t>
+          <t>3 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2176,17 +2176,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Ungradable: 3 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1. Escalation: carcinogen in leave-on.</t>
+          <t>1 flagged ingredient(s) in the printed list (Petrolatum); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Identical printed text on 1 other product(s): Vaseline® Lip Therapy® Crème Brûlée Mini. D7: ungradable. Two or more unknown ingredients remain: Flavor, Theobroma Cacao (Cocoa) Seed Butter, Yellow 5 Lake.</t>
+          <t>Identical printed text on 1 other product(s): Vaseline® Lip Therapy® Crème Brûlée Mini. 3 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Ungradable: 3 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1. Escalation: carcinogen in leave-on.</t>
+          <t>1 flagged ingredient(s) in the printed list (Petrolatum); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Identical printed text on 1 other product(s): Vaseline® Lip Therapy® Cocoa Butter Mini. D7: ungradable. Two or more unknown ingredients remain: Flavor, Theobroma Cacao (Cocoa) Seed Butter, Yellow 5 Lake.</t>
+          <t>Identical printed text on 1 other product(s): Vaseline® Lip Therapy® Cocoa Butter Mini. 3 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2308,17 +2308,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Dimethicone, Phenoxyethanol, Methylparaben); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Isopropyl Myristate, Sorbitan Isostearate, Tapioca Starch, Stearic Acid, Ammonium Acryloyldimethyltaurate/VP Copolymer, Disodium EDTA, Aloe Barbadensis Leaf Juice Powder.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2374,17 +2374,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Dimethicone, Phenoxyethanol, Fragrance (Parfum)); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Isopropyl Myristate, Sorbitan Isostearate, Tapioca Starch, Stearic Acid, Ammonium Acryloyldimethyltaurate/Vp Copolymer, Disodium Edta, Theobroma Cacao (Cocoa) Seed Butter.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1. Escalation: carcinogen in leave-on.</t>
+          <t>1 flagged ingredient(s) in the printed list (Petrolatum); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Microcrystalline Wax, Caprylic/Capric Triglyceride, Ricinus Communis (Castor) Seed Oil, Polyglyceryl-3 Distearate, Butyrospermum Parkii (Shea) Butter, Copernicia Cerifera (Carnauba) Wax, C20-40 Alkyl Stearate, Tocopheryl Acetate.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2506,17 +2506,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Petrolatum, Vaccinium Macrocarpon (Cranberry) Fruit Extract, Butylene Glycol); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Audit notes: Printed carnauba INCI reads 'Camauba' on the page; kept as printed. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Microcrystalline Wax, Caprylic/Capric Triglyceride, Ricinus Communis (Castor) Seed Oil, Polyglyceryl-3 Distearate, Butyrospermum Parkii (Shea) Butter, Copernicia Cerifera (Camauba) Wax, C20-40 Alkyl Stearate, Tocopheryl Acetate, Rose Flower Oil, Olea Europaea (Olive) Fruit Oil, Prunus Amygdalus Dulcis (Sweet Almond) Oil, Rubus Idaeus (Raspberry) Fruit Extract, Red 7 Lake (Ci 15850).</t>
+          <t>Audit notes: Printed carnauba INCI reads 'Camauba' on the page; kept as printed. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2572,17 +2572,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Petrolatum, Butylene Glycol, Fragrance); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Microcrystalline Wax, Caprylic/Capric Triglyceride, Ricinus Communis (Castor) Seed Oil, Polyglyceryl-3 Distearate, Butyrospermum Parkii (Shea) Butter, Copernicia Cerifera (Carnauba) Wax, C20-40 Alkyl Stearate, Tocopheryl Acetate, Persea Gratissima (Avocado) Oil, Camellia Sinensis Leaf Extract, Aloe Barbadensis Leaf Extract.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2638,17 +2638,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Petrolatum, Butylene Glycol, Fragrance); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Microcrystalline Wax, Caprylic Triglyceride, Ricinus Communis (Castor) Seed Oil, Polyglyceryl-3 Distearate, Shea Butter, Cocoa Seed Butter, Carnauba Wax, C20-40 Alkyl Stearate, Tocopheryl Acetate, Jojoba Seed Oil, Camellia Sinensis Leaf Extract, Avocado Fruit Extract, Macadamia Integrifolia Seed Oil. Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1. Escalation: carcinogen in leave-on.</t>
+          <t>1 flagged ingredient(s) in the printed list (Petrolatum); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>D7: ungradable. Two or more unknown ingredients remain: Flavor (Aroma), Red 30 (Ci 73360).</t>
+          <t>2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2820,17 +2820,17 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, Fragrance (Parfum), Coumarin); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Audit notes: Product name printed on the page h1 omits the Vaseline brand prefix; listing name used. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D7: ungradable. Two or more unknown ingredients remain: Hydrogenated Styrene/Butadiene Copolymer, Helianthus Annuus (Sunflower) Seed Oil, Stearic Acid, Theobroma Cacao (Cocoa) Seed Butter, Calcium Sodium Borosilicate, Benzyl Benzoate, Hexyl Cinnamal, Tin Oxide (CI 77861).</t>
+          <t>Audit notes: Product name printed on the page h1 omits the Vaseline brand prefix; listing name used. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2886,17 +2886,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>8 flagged ingredient(s) in the printed list (Mineral Oil, Fragrance (Parfum), Silica); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Audit notes: Product name printed on the page h1 omits the Vaseline brand prefix; listing name used. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. D7: ungradable. Two or more unknown ingredients remain: Hydrogenated Styrene/Butadiene Copolymer, Helianthus Annuus (Sunflower) Seed Oil, Stearic Acid, Theobroma Cacao (Cocoa) Seed Butter, Calcium Sodium Borosilicate, Calcium Aluminum Borosilicate, Benzyl Benzoate, Hexyl Cinnamal, Tin Oxide (CI 77861).</t>
+          <t>Audit notes: Product name printed on the page h1 omits the Vaseline brand prefix; listing name used. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3402,17 +3402,17 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s) in the printed list (Mineral Oil, Fragrance); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>D7: ungradable. Two or more unknown ingredients remain: Hydrogenated Styrene/Butadiene Copolymer, Theobroma Cacao (Cocoa) Seed Butter.</t>
+          <t>2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3568,17 +3568,17 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Ungradable: 15 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>8 flagged ingredient(s) in the printed list (Dimethicone, Carbomer, Phenoxyethanol); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Isohexadecane, Stearic Acid, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium Edta, Helianthus Annuus (Sunflower) Seed Oil, Glycine, Sodium Pca, Cystine, Rutin, Palmitoyl Tripeptide-1, Palmitoyl Tetrapeptide-7, Phaseolus Lunatus (Green Bean) Seed Extract, Benzyl Salicylate, Citronellol, Hexyl Cinnamal.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3634,17 +3634,17 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Ungradable: 13 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Dimethicone, Carbomer, Phenoxyethanol); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Isohexadecane, Stearic Acid, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium Edta, Helianthus Annuus (Sunflower) Seed Oil, Glycine, Sodium Pca, Cystine, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, Benzyl Salicylate, Citronellol, Hexyl Cinnamal.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 13 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>

--- a/audits/vaseline/vaseline_audit.xlsx
+++ b/audits/vaseline/vaseline_audit.xlsx
@@ -745,7 +745,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>6 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>6 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>1 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). 6 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). 6 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>3 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Audit notes: Ingredient list as printed on the product page ends mid-word at 'PROPYLP'. The page's own data layer carries the same truncated string, so the remainder of the list is not captured. Manual re-check needed against the physical package or the brand's SmartLabel before grading is final. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Audit notes: Ingredient list as printed on the product page ends mid-word at 'PROPYLP'. The page's own data layer carries the same truncated string, so the remainder of the list is not captured. Manual re-check needed against the physical package or the brand's SmartLabel before grading is final. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 13 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 13 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 23 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 23 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>1 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>3 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>3 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Identical printed text on 1 other product(s): Vaseline® Lip Therapy® Crème Brûlée Mini. 3 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Identical printed text on 1 other product(s): Vaseline® Lip Therapy® Crème Brûlée Mini. 3 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Identical printed text on 1 other product(s): Vaseline® Lip Therapy® Cocoa Butter Mini. 3 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Identical printed text on 1 other product(s): Vaseline® Lip Therapy® Cocoa Butter Mini. 3 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Audit notes: Printed carnauba INCI reads 'Camauba' on the page; kept as printed. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Audit notes: Printed carnauba INCI reads 'Camauba' on the page; kept as printed. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17). Iron oxides (reference cat. 1, 2, 3): heavy-metal (cat. 3) escalation applies; PFAS-treated tag applied as written.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>2 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Audit notes: Product name printed on the page h1 omits the Vaseline brand prefix; listing name used. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Audit notes: Product name printed on the page h1 omits the Vaseline brand prefix; listing name used. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. 8 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Audit notes: Product name printed on the page h1 omits the Vaseline brand prefix; listing name used. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Audit notes: Product name printed on the page h1 omits the Vaseline brand prefix; listing name used. Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D1: unspecified silica does not trigger the PFAS-treated escalation. 9 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>2 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 13 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 13 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">

--- a/audits/vaseline/vaseline_audit.xlsx
+++ b/audits/vaseline/vaseline_audit.xlsx
@@ -999,17 +999,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>12 flagged ingredient(s) in the printed list (Dimethicone, Dipropylene Glycol, Ceteth-20); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>12 flagged ingredient(s) in the printed list (Dimethicone, Dipropylene Glycol, Ceteth-20); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Propylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1379,17 +1379,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>9 flagged ingredient(s) in the printed list (PETROLATUM, TRIETHANOLAMINE, PHENOXYETHANOL); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>9 flagged ingredient(s) in the printed list (PETROLATUM, TRIETHANOLAMINE, PHENOXYETHANOL); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): METHYLPARABEN, PROPYLPARABEN in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1445,17 +1445,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>13 flagged ingredient(s) in the printed list (PETROLATUM, DIMETHICONE, BUTYLENE GLYCOL); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>13 flagged ingredient(s) in the printed list (PETROLATUM, DIMETHICONE, BUTYLENE GLYCOL); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): METHYLPARABEN, PROPYLPARABEN in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>12 flagged ingredient(s) in the printed list (DIMETHICONE, PEG-100 STEARATE, PETROLATUM); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>12 flagged ingredient(s) in the printed list (DIMETHICONE, PEG-100 STEARATE, PETROLATUM); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): METHYLPARABEN, PROPYLPARABEN in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1577,17 +1577,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>12 flagged ingredient(s) in the printed list (MINERAL OIL, DIMETHICONE, PEG-100 STEARATE); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>12 flagged ingredient(s) in the printed list (MINERAL OIL, DIMETHICONE, PEG-100 STEARATE); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): METHYLPARABEN, PROPYLPARABEN in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (PEG-100 STEARATE, DIMETHICONE, MINERAL OIL); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (PEG-100 STEARATE, DIMETHICONE, MINERAL OIL); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Audit notes: Ingredient list as printed on the product page ends mid-word at 'PROPYLP'. The page's own data layer carries the same truncated string, so the remainder of the list is not captured. Manual re-check needed against the physical package or the brand's SmartLabel before grading is final. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>Audit notes: Ingredient list as printed on the product page ends mid-word at 'PROPYLP'. The page's own data layer carries the same truncated string, so the remainder of the list is not captured. Manual re-check needed against the physical package or the brand's SmartLabel before grading is final. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): METHYLPARABEN in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1709,17 +1709,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>10 flagged ingredient(s) in the printed list (Petrolatum, Dimethicone, Triethanolamine); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>10 flagged ingredient(s) in the printed list (Petrolatum, Dimethicone, Triethanolamine); tier applies to the printed subset only. 15 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 15 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Propylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1775,17 +1775,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>11 flagged ingredient(s) in the printed list (Petrolatum, Triethanolamine, Dimethicone); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>11 flagged ingredient(s) in the printed list (Petrolatum, Triethanolamine, Dimethicone); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 13 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 13 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Propylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>16 flagged ingredient(s) in the printed list (Petrolatum, Dimethicone, Cyclopentasiloxane); tier applies to the printed subset only. 23 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>16 flagged ingredient(s) in the printed list (Petrolatum, Dimethicone, Cyclopentasiloxane); tier applies to the printed subset only. 23 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 23 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 23 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Propylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1907,17 +1907,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>10 flagged ingredient(s) in the printed list (Mineral Oil (Huile Minérale), Dimethicone, PEG-100 Stearate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>10 flagged ingredient(s) in the printed list (Mineral Oil (Huile Minérale), Dimethicone, PEG-100 Stearate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Propylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1973,17 +1973,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>11 flagged ingredient(s) in the printed list (PEG-100 Stearate, Dimethicone, Mineral Oil (Huile Minérale)); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>11 flagged ingredient(s) in the printed list (PEG-100 Stearate, Dimethicone, Mineral Oil (Huile Minérale)); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Propylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2303,17 +2303,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Dimethicone, Phenoxyethanol, Methylparaben); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Dimethicone, Phenoxyethanol, Methylparaben); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Propylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2369,17 +2369,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Dimethicone, Phenoxyethanol, Fragrance (Parfum)); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Dimethicone, Phenoxyethanol, Fragrance (Parfum)); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Propylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
